--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484636_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484636_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6635</v>
+        <v>2.5386</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6096</v>
+        <v>3.8388</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9461</v>
+        <v>-1.3002</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.4232</v>
+        <v>4.0365</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2079</v>
+        <v>-1.2497</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.2152</v>
+        <v>5.2863</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8148</v>
+        <v>6.0944</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5231</v>
+        <v>0.8079</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2917</v>
+        <v>5.2866</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.238</v>
+        <v>-2.0579</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7311</v>
+        <v>-2.0576</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.5069</v>
+        <v>-0.0003</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.1991</v>
+        <v>-0.733</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7964</v>
+        <v>-0.7649</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6931</v>
+        <v>-0.4231</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1033</v>
+        <v>-0.3418</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4894</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>4.7668</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6227</v>
+        <v>0.4678</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3441</v>
+        <v>2.9093</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7214</v>
+        <v>-2.4415</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0365</v>
+        <v>-1.4232</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2497</v>
+        <v>-0.2079</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2863</v>
+        <v>-1.2152</v>
       </c>
       <c r="J3" t="n">
-        <v>6.0944</v>
+        <v>1.8148</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8079</v>
+        <v>1.5231</v>
       </c>
       <c r="L3" t="n">
-        <v>5.2866</v>
+        <v>0.2917</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0579</v>
+        <v>-3.238</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0576</v>
+        <v>-1.7311</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0003</v>
+        <v>-1.5069</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.733</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6808</v>
+        <v>0.6007</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.0071</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.763</v>
+        <v>0.6078</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.4894</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4.7668</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2774</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1343</v>
+        <v>-0.0574</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9646</v>
+        <v>1.1159</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0989</v>
+        <v>-1.1732</v>
       </c>
       <c r="G4" t="n">
         <v>-2.1346</v>
@@ -766,13 +766,13 @@
         <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.852</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8627</v>
+        <v>-0.7115</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.1405</v>
       </c>
       <c r="V4" t="n">
         <v>3.479</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.142</v>
+        <v>-1.0925</v>
       </c>
       <c r="E5" t="n">
         <v>-0.7645</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3775</v>
+        <v>-0.328</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1932</v>
@@ -844,13 +844,13 @@
         <v>0.1833</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1321</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U5" t="n">
-        <v>0.033</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5531</v>
+        <v>-1.2393</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3161</v>
+        <v>-0.151</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.237</v>
+        <v>-1.0884</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1779</v>
@@ -922,13 +922,13 @@
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.3571</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4789</v>
+        <v>-0.3137</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.192</v>
+        <v>-0.0434</v>
       </c>
       <c r="V6" t="n">
         <v>1.5785</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8148</v>
+        <v>-1.8644</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7628</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.052</v>
+        <v>-1.1015</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4968</v>
@@ -1000,13 +1000,13 @@
         <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1793</v>
+        <v>-0.2289</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0142</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3219</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6098</v>
+        <v>-2.6375</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1721</v>
+        <v>-2.076</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4377</v>
+        <v>-0.5615</v>
       </c>
       <c r="G8" t="n">
         <v>-2.7664</v>
@@ -1078,13 +1078,13 @@
         <v>0.5498</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0999</v>
+        <v>-0.1276</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3122</v>
+        <v>-0.2161</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2123</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0.6231</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1725</v>
+        <v>-3.3097</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8417</v>
+        <v>-1.9789</v>
       </c>
       <c r="F9" t="n">
         <v>-1.3308</v>
@@ -1156,10 +1156,10 @@
         <v>0.9163</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4035</v>
+        <v>-0.5407</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2398</v>
+        <v>-0.3771</v>
       </c>
       <c r="U9" t="n">
         <v>-0.1637</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1816</v>
+        <v>-3.3903</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.006</v>
+        <v>-1.2394</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1757</v>
+        <v>-2.1509</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9862</v>
@@ -1234,13 +1234,13 @@
         <v>0.733</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1117</v>
+        <v>-0.3203</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0355</v>
+        <v>-0.198</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1471</v>
+        <v>-0.1224</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9005</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2582</v>
+        <v>-3.4665</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4149</v>
+        <v>-1.6728</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8433</v>
+        <v>-1.7937</v>
       </c>
       <c r="G11" t="n">
         <v>-5.5423</v>
@@ -1312,13 +1312,13 @@
         <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8833</v>
+        <v>-0.0916</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.23</v>
+        <v>-0.4879</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3467</v>
+        <v>0.3963</v>
       </c>
       <c r="V11" t="n">
         <v>2.5339</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1648</v>
+        <v>-4.8678</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8788</v>
+        <v>-3.6314</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.286</v>
+        <v>-1.2364</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6035</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4617</v>
+        <v>-0.1648</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5875</v>
+        <v>-0.3401</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1258</v>
+        <v>0.1753</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.7449</v>
+        <v>-18.919</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.2386</v>
+        <v>-4.412800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.5064</v>
+        <v>-14.5061</v>
       </c>
       <c r="G13" t="n">
         <v>-18.4231</v>
@@ -1468,13 +1468,13 @@
         <v>10.0793</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.7557</v>
+        <v>-2.9298</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.2307</v>
+        <v>-3.405</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4748999999999999</v>
+        <v>0.4749</v>
       </c>
       <c r="V13" t="n">
         <v>8.848000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8837</v>
+        <v>6.9712</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8393</v>
+        <v>4.5508</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0445</v>
+        <v>2.4204</v>
       </c>
       <c r="G14" t="n">
         <v>4.2142</v>
@@ -1546,13 +1546,13 @@
         <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6591</v>
+        <v>0.7466</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5475</v>
+        <v>0.2591</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1116</v>
+        <v>0.4875</v>
       </c>
       <c r="V14" t="n">
         <v>1.2774</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9546</v>
+        <v>5.9182</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3887</v>
+        <v>5.1003</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5658</v>
+        <v>0.8179</v>
       </c>
       <c r="G15" t="n">
         <v>3.268</v>
@@ -1624,13 +1624,13 @@
         <v>1.2828</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4483</v>
+        <v>0.412</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2187</v>
+        <v>-0.0697</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2296</v>
+        <v>0.4817</v>
       </c>
       <c r="V15" t="n">
         <v>0.9554</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.626</v>
+        <v>5.8899</v>
       </c>
       <c r="E16" t="n">
-        <v>3.605</v>
+        <v>5.2502</v>
       </c>
       <c r="F16" t="n">
-        <v>2.021</v>
+        <v>0.6397</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9808</v>
+        <v>4.863</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9939</v>
+        <v>-0.5738</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.013</v>
+        <v>5.4368</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9814</v>
+        <v>6.1805</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8981</v>
+        <v>0.2627</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0833</v>
+        <v>5.9177</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9994</v>
+        <v>-1.3175</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0958</v>
+        <v>-0.8365</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0964</v>
+        <v>-0.481</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9017</v>
+        <v>0.3384</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5294</v>
+        <v>-0.1527</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3723</v>
+        <v>0.4911</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2566</v>
+        <v>0.3219</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0104</v>
+        <v>0.3219</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.2998</v>
+        <v>4.5084</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9617</v>
+        <v>3.0281</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3381</v>
+        <v>1.4803</v>
       </c>
       <c r="G17" t="n">
-        <v>4.863</v>
+        <v>4.9808</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5738</v>
+        <v>4.9939</v>
       </c>
       <c r="I17" t="n">
-        <v>5.4368</v>
+        <v>-0.013</v>
       </c>
       <c r="J17" t="n">
-        <v>6.1805</v>
+        <v>3.9814</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2627</v>
+        <v>3.8981</v>
       </c>
       <c r="L17" t="n">
-        <v>5.9177</v>
+        <v>0.0833</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3175</v>
+        <v>0.9994</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8365</v>
+        <v>1.0958</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.481</v>
+        <v>-0.0964</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2517</v>
+        <v>0.7841</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4412</v>
+        <v>-0.0475</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1895</v>
+        <v>0.8316</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3219</v>
+        <v>-1.2566</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3219</v>
+        <v>0.0104</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0185</v>
+        <v>2.6989</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2825</v>
+        <v>-0.7056</v>
       </c>
       <c r="F18" t="n">
-        <v>3.301</v>
+        <v>3.4044</v>
       </c>
       <c r="G18" t="n">
         <v>1.55</v>
@@ -1858,13 +1858,13 @@
         <v>2.3823</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4924</v>
+        <v>0.188</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1199</v>
+        <v>-0.543</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.7309</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3219</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5031</v>
+        <v>2.1878</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0649</v>
+        <v>0.6419</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4381</v>
+        <v>1.5459</v>
       </c>
       <c r="G19" t="n">
         <v>2.1716</v>
@@ -1936,13 +1936,13 @@
         <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3178</v>
+        <v>0.3669</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8077</v>
+        <v>-0.2307</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4899</v>
+        <v>0.5976</v>
       </c>
       <c r="V19" t="n">
         <v>-1.267</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9906</v>
+        <v>1.3417</v>
       </c>
       <c r="E20" t="n">
         <v>-2.059</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0496</v>
+        <v>3.4008</v>
       </c>
       <c r="G20" t="n">
         <v>0.3195</v>
@@ -2014,13 +2014,13 @@
         <v>2.5656</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4224</v>
+        <v>0.7736</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0022</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4246</v>
+        <v>0.7758</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3011</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.47</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2377</v>
+        <v>-0.0454</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7077</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0421</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4333</v>
+        <v>0.477</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6535</v>
+        <v>0.5049</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6543</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5255</v>
+        <v>-0.9101</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6753</v>
+        <v>-1.0599</v>
       </c>
       <c r="F22" t="n">
         <v>0.1498</v>
@@ -2170,10 +2170,10 @@
         <v>0.3665</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8424</v>
+        <v>0.4578</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8424</v>
+        <v>0.4578</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1787</v>
+        <v>-1.1904</v>
       </c>
       <c r="E23" t="n">
-        <v>1.871</v>
+        <v>1.5825</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0497</v>
+        <v>-2.7729</v>
       </c>
       <c r="G23" t="n">
         <v>1.5132</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.103</v>
+        <v>-0.1146</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2557</v>
+        <v>-0.0328</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3587</v>
+        <v>-0.0818</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2224</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.484</v>
+        <v>-2.7977</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9344</v>
+        <v>-2.5498</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5496</v>
+        <v>-0.2479</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1773</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.49</v>
+        <v>0.1963</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3492</v>
+        <v>0.0355</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1408</v>
+        <v>0.1608</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8132</v>
+        <v>-4.1046</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9645</v>
+        <v>0.7722</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.7776</v>
+        <v>-4.8767</v>
       </c>
       <c r="G25" t="n">
         <v>-1.0428</v>
@@ -2404,13 +2404,13 @@
         <v>1.4661</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7032</v>
+        <v>0.4118</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0717</v>
+        <v>-0.1206</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6315</v>
+        <v>0.5324</v>
       </c>
       <c r="V25" t="n">
         <v>-4.7563</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>19.74489999999999</v>
+        <v>21.0269</v>
       </c>
       <c r="E26" t="n">
-        <v>14.5062</v>
+        <v>14.5063</v>
       </c>
       <c r="F26" t="n">
-        <v>5.238700000000003</v>
+        <v>6.520700000000001</v>
       </c>
       <c r="G26" t="n">
         <v>18.42300000000001</v>
@@ -2482,13 +2482,13 @@
         <v>16.4932</v>
       </c>
       <c r="S26" t="n">
-        <v>3.7555</v>
+        <v>5.0379</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4749999999999999</v>
+        <v>-0.4747</v>
       </c>
       <c r="U26" t="n">
-        <v>4.230499999999999</v>
+        <v>5.512499999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-8.847999999999999</v>
